--- a/data/habits.xlsx
+++ b/data/habits.xlsx
@@ -8,13 +8,15 @@
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Habits" state="visible" r:id="rId4"/>
+    <sheet sheetId="3" name="2026-09" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="2026-08" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="124">
   <si>
     <t>Habit ID</t>
   </si>
@@ -85,10 +87,10 @@
     <t>[]</t>
   </si>
   <si>
-    <t>2026-08-09T05:02:54.909Z</t>
-  </si>
-  <si>
-    <t>{"2026-09-28":false,"2026-09-27":false,"2026-09-26":false,"2026-09-25":false,"2026-09-24":false,"2026-09-23":false,"2026-09-22":false,"2026-09-21":false,"2026-09-20":false,"2026-09-19":false,"2026-09-18":false,"2026-09-17":false,"2026-09-16":false,"2026-09-15":false,"2026-09-14":false,"2026-09-13":false,"2026-09-12":false,"2026-09-11":false,"2026-09-10":false,"2026-09-09":false,"2026-09-08":false,"2026-09-07":false,"2026-09-06":false,"2026-09-05":false,"2026-09-04":false,"2026-09-03":false,"2026-09-02":false,"2026-09-01":false,"2026-08-31":false,"2026-08-30":false,"2026-08-29":false,"2026-08-28":false,"2026-08-27":false,"2026-08-26":false,"2026-08-25":false,"2026-08-24":false,"2026-08-23":false,"2026-08-22":false,"2026-08-21":false,"2026-08-20":false,"2026-08-19":false,"2026-08-18":false,"2026-08-17":false,"2026-08-16":false,"2026-08-15":false,"2026-08-14":false,"2026-08-13":false,"2026-08-12":false}</t>
+    <t>2026-08-09T15:08:05.372Z</t>
+  </si>
+  <si>
+    <t>{"2026-09-28":true,"2026-09-27":true,"2026-09-26":true,"2026-09-25":false,"2026-09-24":true,"2026-09-23":true,"2026-09-22":true,"2026-09-21":false,"2026-09-20":true,"2026-09-19":true,"2026-09-18":false,"2026-09-17":true,"2026-09-16":true,"2026-09-15":false,"2026-09-14":true,"2026-09-13":true,"2026-09-12":true,"2026-09-11":false,"2026-09-10":true,"2026-09-09":true,"2026-09-08":false,"2026-09-07":true,"2026-09-06":true,"2026-09-05":false,"2026-09-04":true,"2026-09-03":true,"2026-09-02":true,"2026-09-01":false,"2026-08-31":true,"2026-08-30":true,"2026-08-29":false,"2026-08-28":true,"2026-08-27":true,"2026-08-26":false,"2026-08-25":true,"2026-08-24":true,"2026-08-23":true,"2026-08-22":false,"2026-08-21":true,"2026-08-20":true,"2026-08-19":false,"2026-08-18":true,"2026-08-17":true,"2026-08-16":false,"2026-08-15":true,"2026-08-14":true,"2026-08-13":true,"2026-08-12":false}</t>
   </si>
   <si>
     <t>reading</t>
@@ -109,7 +111,10 @@
     <t>#7c70d8</t>
   </si>
   <si>
-    <t>2026-08-09T05:02:54.911Z</t>
+    <t>2026-08-09T15:08:05.376Z</t>
+  </si>
+  <si>
+    <t>{"2026-09-28":true,"2026-09-27":true,"2026-09-26":true,"2026-09-25":false,"2026-09-24":false,"2026-09-23":true,"2026-09-22":true,"2026-09-21":false,"2026-09-20":true,"2026-09-19":true,"2026-09-18":false,"2026-09-17":true,"2026-09-16":true,"2026-09-15":false,"2026-09-14":false,"2026-09-13":true,"2026-09-12":true,"2026-09-11":false,"2026-09-10":true,"2026-09-09":true,"2026-09-08":false,"2026-09-07":true,"2026-09-06":true,"2026-09-05":false,"2026-09-04":false,"2026-09-03":true,"2026-09-02":true,"2026-09-01":false,"2026-08-31":true,"2026-08-30":true,"2026-08-29":false,"2026-08-28":true,"2026-08-27":true,"2026-08-26":false,"2026-08-25":false,"2026-08-24":true,"2026-08-23":true,"2026-08-22":false,"2026-08-21":true,"2026-08-20":true,"2026-08-19":false,"2026-08-18":true,"2026-08-17":true,"2026-08-16":false,"2026-08-15":false,"2026-08-14":true,"2026-08-13":true,"2026-08-12":false}</t>
   </si>
   <si>
     <t>meditation</t>
@@ -130,7 +135,7 @@
     <t>#3e9d8b</t>
   </si>
   <si>
-    <t>2026-08-09T05:02:54.912Z</t>
+    <t>{"2026-09-28":true,"2026-09-27":false,"2026-09-26":true,"2026-09-25":true,"2026-09-24":false,"2026-09-23":true,"2026-09-22":true,"2026-09-21":true,"2026-09-20":true,"2026-09-19":true,"2026-09-18":true,"2026-09-17":false,"2026-09-16":true,"2026-09-15":true,"2026-09-14":false,"2026-09-13":true,"2026-09-12":true,"2026-09-11":true,"2026-09-10":true,"2026-09-09":true,"2026-09-08":true,"2026-09-07":false,"2026-09-06":true,"2026-09-05":true,"2026-09-04":false,"2026-09-03":true,"2026-09-02":true,"2026-09-01":true,"2026-08-31":true,"2026-08-30":true,"2026-08-29":true,"2026-08-28":false,"2026-08-27":true,"2026-08-26":true,"2026-08-25":false,"2026-08-24":true,"2026-08-23":true,"2026-08-22":true,"2026-08-21":true,"2026-08-20":true,"2026-08-19":true,"2026-08-18":false,"2026-08-17":true,"2026-08-16":true,"2026-08-15":false,"2026-08-14":true,"2026-08-13":true,"2026-08-12":true}</t>
   </si>
   <si>
     <t>water</t>
@@ -151,7 +156,7 @@
     <t>#4b8dcc</t>
   </si>
   <si>
-    <t>2026-08-09T05:02:54.913Z</t>
+    <t>{"2026-09-28":true,"2026-09-27":false,"2026-09-26":true,"2026-09-25":true,"2026-09-24":false,"2026-09-23":true,"2026-09-22":true,"2026-09-21":true,"2026-09-20":false,"2026-09-19":true,"2026-09-18":true,"2026-09-17":false,"2026-09-16":true,"2026-09-15":true,"2026-09-14":false,"2026-09-13":true,"2026-09-12":true,"2026-09-11":true,"2026-09-10":false,"2026-09-09":true,"2026-09-08":true,"2026-09-07":false,"2026-09-06":true,"2026-09-05":true,"2026-09-04":false,"2026-09-03":true,"2026-09-02":true,"2026-09-01":true,"2026-08-31":false,"2026-08-30":true,"2026-08-29":true,"2026-08-28":false,"2026-08-27":true,"2026-08-26":true,"2026-08-25":false,"2026-08-24":true,"2026-08-23":true,"2026-08-22":true,"2026-08-21":false,"2026-08-20":true,"2026-08-19":true,"2026-08-18":false,"2026-08-17":true,"2026-08-16":true,"2026-08-15":false,"2026-08-14":true,"2026-08-13":true,"2026-08-12":true}</t>
   </si>
   <si>
     <t>deep-work</t>
@@ -175,7 +180,10 @@
     <t>weekdays</t>
   </si>
   <si>
-    <t>2026-08-09T05:02:54.915Z</t>
+    <t>2026-08-09T15:08:05.377Z</t>
+  </si>
+  <si>
+    <t>{"2026-09-28":true,"2026-09-27":false,"2026-09-26":true,"2026-09-25":true,"2026-09-24":false,"2026-09-23":false,"2026-09-22":true,"2026-09-21":true,"2026-09-20":false,"2026-09-19":true,"2026-09-18":true,"2026-09-17":false,"2026-09-16":true,"2026-09-15":true,"2026-09-14":false,"2026-09-13":false,"2026-09-12":true,"2026-09-11":true,"2026-09-10":false,"2026-09-09":true,"2026-09-08":true,"2026-09-07":false,"2026-09-06":true,"2026-09-05":true,"2026-09-04":false,"2026-09-03":false,"2026-09-02":true,"2026-09-01":true,"2026-08-31":false,"2026-08-30":true,"2026-08-29":true,"2026-08-28":false,"2026-08-27":true,"2026-08-26":true,"2026-08-25":false,"2026-08-24":false,"2026-08-23":true,"2026-08-22":true,"2026-08-21":false,"2026-08-20":true,"2026-08-19":true,"2026-08-18":false,"2026-08-17":true,"2026-08-16":true,"2026-08-15":false,"2026-08-14":false,"2026-08-13":true,"2026-08-12":true}</t>
   </si>
   <si>
     <t>typescript</t>
@@ -193,7 +201,7 @@
     <t>#4778b9</t>
   </si>
   <si>
-    <t>2026-08-09T05:02:54.916Z</t>
+    <t>{"2026-09-28":true,"2026-09-27":true,"2026-09-26":false,"2026-09-25":true,"2026-09-24":true,"2026-09-23":false,"2026-09-22":true,"2026-09-21":true,"2026-09-20":true,"2026-09-19":true,"2026-09-18":true,"2026-09-17":true,"2026-09-16":false,"2026-09-15":true,"2026-09-14":true,"2026-09-13":false,"2026-09-12":true,"2026-09-11":true,"2026-09-10":true,"2026-09-09":true,"2026-09-08":true,"2026-09-07":true,"2026-09-06":false,"2026-09-05":true,"2026-09-04":true,"2026-09-03":false,"2026-09-02":true,"2026-09-01":true,"2026-08-31":true,"2026-08-30":true,"2026-08-29":true,"2026-08-28":true,"2026-08-27":false,"2026-08-26":true,"2026-08-25":true,"2026-08-24":false,"2026-08-23":true,"2026-08-22":true,"2026-08-21":true,"2026-08-20":true,"2026-08-19":true,"2026-08-18":true,"2026-08-17":false,"2026-08-16":true,"2026-08-15":true,"2026-08-14":false,"2026-08-13":true,"2026-08-12":true}</t>
   </si>
   <si>
     <t>sleep</t>
@@ -212,6 +220,174 @@
   </si>
   <si>
     <t>#926fc1</t>
+  </si>
+  <si>
+    <t>{"2026-09-28":true,"2026-09-27":true,"2026-09-26":false,"2026-09-25":true,"2026-09-24":true,"2026-09-23":false,"2026-09-22":true,"2026-09-21":true,"2026-09-20":true,"2026-09-19":false,"2026-09-18":true,"2026-09-17":true,"2026-09-16":false,"2026-09-15":true,"2026-09-14":true,"2026-09-13":false,"2026-09-12":true,"2026-09-11":true,"2026-09-10":true,"2026-09-09":false,"2026-09-08":true,"2026-09-07":true,"2026-09-06":false,"2026-09-05":true,"2026-09-04":true,"2026-09-03":false,"2026-09-02":true,"2026-09-01":true,"2026-08-31":true,"2026-08-30":false,"2026-08-29":true,"2026-08-28":true,"2026-08-27":false,"2026-08-26":true,"2026-08-25":true,"2026-08-24":false,"2026-08-23":true,"2026-08-22":true,"2026-08-21":true,"2026-08-20":false,"2026-08-19":true,"2026-08-18":true,"2026-08-17":false,"2026-08-16":true,"2026-08-15":true,"2026-08-14":false,"2026-08-13":true,"2026-08-12":true}</t>
+  </si>
+  <si>
+    <t>habit-1790608579846</t>
+  </si>
+  <si>
+    <t>Loudly speak English</t>
+  </si>
+  <si>
+    <t>2026-09-28T15:16:19.846Z</t>
+  </si>
+  <si>
+    <t>{"2026-09-28":true}</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Habit</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
   </si>
 </sst>
 </file>
@@ -588,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -733,27 +909,27 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -765,7 +941,7 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -774,27 +950,27 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
@@ -806,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -815,30 +991,30 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -847,7 +1023,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
@@ -856,30 +1032,30 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -888,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
@@ -897,27 +1073,27 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
         <v>21</v>
@@ -929,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
@@ -938,7 +1114,3425 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>24</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D99"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" t="s">
+        <v>41</v>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>63</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>116</v>
+      </c>
+      <c r="B64" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>116</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>116</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>117</v>
+      </c>
+      <c r="B68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" t="s">
+        <v>63</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>118</v>
+      </c>
+      <c r="B70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" t="s">
+        <v>48</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>118</v>
+      </c>
+      <c r="B71" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" t="s">
+        <v>41</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>118</v>
+      </c>
+      <c r="B72" t="s">
+        <v>56</v>
+      </c>
+      <c r="C72" t="s">
+        <v>57</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>118</v>
+      </c>
+      <c r="B73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>118</v>
+      </c>
+      <c r="B74" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" t="s">
+        <v>63</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>119</v>
+      </c>
+      <c r="B75" t="s">
+        <v>47</v>
+      </c>
+      <c r="C75" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>119</v>
+      </c>
+      <c r="B76" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>119</v>
+      </c>
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>119</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>120</v>
+      </c>
+      <c r="B80" t="s">
+        <v>56</v>
+      </c>
+      <c r="C80" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>120</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>120</v>
+      </c>
+      <c r="B82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B83" t="s">
+        <v>62</v>
+      </c>
+      <c r="C83" t="s">
+        <v>63</v>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>121</v>
+      </c>
+      <c r="B84" t="s">
+        <v>47</v>
+      </c>
+      <c r="C84" t="s">
+        <v>48</v>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>121</v>
+      </c>
+      <c r="B85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" t="s">
+        <v>41</v>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>121</v>
+      </c>
+      <c r="B86" t="s">
+        <v>56</v>
+      </c>
+      <c r="C86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>121</v>
+      </c>
+      <c r="B87" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>121</v>
+      </c>
+      <c r="B88" t="s">
+        <v>62</v>
+      </c>
+      <c r="C88" t="s">
+        <v>63</v>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>122</v>
+      </c>
+      <c r="B89" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" t="s">
+        <v>48</v>
+      </c>
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>122</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90" t="s">
+        <v>41</v>
+      </c>
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>122</v>
+      </c>
+      <c r="B91" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>122</v>
+      </c>
+      <c r="B92" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>122</v>
+      </c>
+      <c r="B93" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>122</v>
+      </c>
+      <c r="B94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" t="s">
+        <v>26</v>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>123</v>
+      </c>
+      <c r="B95" t="s">
+        <v>56</v>
+      </c>
+      <c r="C95" t="s">
+        <v>57</v>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" t="s">
+        <v>33</v>
+      </c>
+      <c r="C96" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>123</v>
+      </c>
+      <c r="B97" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>123</v>
+      </c>
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" t="s">
+        <v>26</v>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>123</v>
+      </c>
+      <c r="B99" t="s">
+        <v>62</v>
+      </c>
+      <c r="C99" t="s">
+        <v>63</v>
+      </c>
+      <c r="D99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D140"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" t="s">
+        <v>41</v>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>63</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>87</v>
+      </c>
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>87</v>
+      </c>
+      <c r="B59" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>88</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>89</v>
+      </c>
+      <c r="B67" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+      <c r="B68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>89</v>
+      </c>
+      <c r="B69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" t="s">
+        <v>63</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>90</v>
+      </c>
+      <c r="B70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" t="s">
+        <v>48</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>90</v>
+      </c>
+      <c r="B71" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" t="s">
+        <v>41</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>90</v>
+      </c>
+      <c r="B72" t="s">
+        <v>56</v>
+      </c>
+      <c r="C72" t="s">
+        <v>57</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" t="s">
+        <v>63</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" t="s">
+        <v>47</v>
+      </c>
+      <c r="C75" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>91</v>
+      </c>
+      <c r="B76" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B77" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" t="s">
+        <v>56</v>
+      </c>
+      <c r="C80" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" t="s">
+        <v>62</v>
+      </c>
+      <c r="C83" t="s">
+        <v>63</v>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84" t="s">
+        <v>47</v>
+      </c>
+      <c r="C84" t="s">
+        <v>48</v>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" t="s">
+        <v>41</v>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" t="s">
+        <v>56</v>
+      </c>
+      <c r="C86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" t="s">
+        <v>62</v>
+      </c>
+      <c r="C88" t="s">
+        <v>63</v>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" t="s">
+        <v>48</v>
+      </c>
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90" t="s">
+        <v>41</v>
+      </c>
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" t="s">
+        <v>26</v>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>56</v>
+      </c>
+      <c r="C95" t="s">
+        <v>57</v>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>33</v>
+      </c>
+      <c r="C96" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>95</v>
+      </c>
+      <c r="B97" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>95</v>
+      </c>
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" t="s">
+        <v>26</v>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>95</v>
+      </c>
+      <c r="B99" t="s">
+        <v>62</v>
+      </c>
+      <c r="C99" t="s">
+        <v>63</v>
+      </c>
+      <c r="D99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>96</v>
+      </c>
+      <c r="B100" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100" t="s">
+        <v>48</v>
+      </c>
+      <c r="D100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>96</v>
+      </c>
+      <c r="B101" t="s">
+        <v>40</v>
+      </c>
+      <c r="C101" t="s">
+        <v>41</v>
+      </c>
+      <c r="D101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>96</v>
+      </c>
+      <c r="B102" t="s">
+        <v>56</v>
+      </c>
+      <c r="C102" t="s">
+        <v>57</v>
+      </c>
+      <c r="D102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>96</v>
+      </c>
+      <c r="B103" t="s">
+        <v>33</v>
+      </c>
+      <c r="C103" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>96</v>
+      </c>
+      <c r="B104" t="s">
+        <v>62</v>
+      </c>
+      <c r="C104" t="s">
+        <v>63</v>
+      </c>
+      <c r="D104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>97</v>
+      </c>
+      <c r="B105" t="s">
+        <v>47</v>
+      </c>
+      <c r="C105" t="s">
+        <v>48</v>
+      </c>
+      <c r="D105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>97</v>
+      </c>
+      <c r="B106" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>97</v>
+      </c>
+      <c r="B107" t="s">
+        <v>56</v>
+      </c>
+      <c r="C107" t="s">
+        <v>57</v>
+      </c>
+      <c r="D107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>97</v>
+      </c>
+      <c r="B108" t="s">
+        <v>33</v>
+      </c>
+      <c r="C108" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>97</v>
+      </c>
+      <c r="B109" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>97</v>
+      </c>
+      <c r="B110" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110" t="s">
+        <v>26</v>
+      </c>
+      <c r="D110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>97</v>
+      </c>
+      <c r="B111" t="s">
+        <v>62</v>
+      </c>
+      <c r="C111" t="s">
+        <v>63</v>
+      </c>
+      <c r="D111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>98</v>
+      </c>
+      <c r="B112" t="s">
+        <v>40</v>
+      </c>
+      <c r="C112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>98</v>
+      </c>
+      <c r="B113" t="s">
+        <v>33</v>
+      </c>
+      <c r="C113" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>98</v>
+      </c>
+      <c r="B114" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>98</v>
+      </c>
+      <c r="B115" t="s">
+        <v>25</v>
+      </c>
+      <c r="C115" t="s">
+        <v>26</v>
+      </c>
+      <c r="D115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>99</v>
+      </c>
+      <c r="B116" t="s">
+        <v>56</v>
+      </c>
+      <c r="C116" t="s">
+        <v>57</v>
+      </c>
+      <c r="D116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>99</v>
+      </c>
+      <c r="B117" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>99</v>
+      </c>
+      <c r="B118" t="s">
+        <v>62</v>
+      </c>
+      <c r="C118" t="s">
+        <v>63</v>
+      </c>
+      <c r="D118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>100</v>
+      </c>
+      <c r="B119" t="s">
+        <v>47</v>
+      </c>
+      <c r="C119" t="s">
+        <v>48</v>
+      </c>
+      <c r="D119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>100</v>
+      </c>
+      <c r="B120" t="s">
+        <v>40</v>
+      </c>
+      <c r="C120" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>100</v>
+      </c>
+      <c r="B121" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121" t="s">
+        <v>57</v>
+      </c>
+      <c r="D121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>100</v>
+      </c>
+      <c r="B122" t="s">
+        <v>33</v>
+      </c>
+      <c r="C122" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>100</v>
+      </c>
+      <c r="B123" t="s">
+        <v>62</v>
+      </c>
+      <c r="C123" t="s">
+        <v>63</v>
+      </c>
+      <c r="D123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>101</v>
+      </c>
+      <c r="B124" t="s">
+        <v>47</v>
+      </c>
+      <c r="C124" t="s">
+        <v>48</v>
+      </c>
+      <c r="D124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>101</v>
+      </c>
+      <c r="B125" t="s">
+        <v>40</v>
+      </c>
+      <c r="C125" t="s">
+        <v>41</v>
+      </c>
+      <c r="D125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>101</v>
+      </c>
+      <c r="B126" t="s">
+        <v>33</v>
+      </c>
+      <c r="C126" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>101</v>
+      </c>
+      <c r="B127" t="s">
+        <v>15</v>
+      </c>
+      <c r="C127" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>101</v>
+      </c>
+      <c r="B128" t="s">
+        <v>25</v>
+      </c>
+      <c r="C128" t="s">
+        <v>26</v>
+      </c>
+      <c r="D128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>102</v>
+      </c>
+      <c r="B129" t="s">
+        <v>56</v>
+      </c>
+      <c r="C129" t="s">
+        <v>57</v>
+      </c>
+      <c r="D129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>102</v>
+      </c>
+      <c r="B130" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>102</v>
+      </c>
+      <c r="B131" t="s">
+        <v>25</v>
+      </c>
+      <c r="C131" t="s">
+        <v>26</v>
+      </c>
+      <c r="D131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>102</v>
+      </c>
+      <c r="B132" t="s">
+        <v>62</v>
+      </c>
+      <c r="C132" t="s">
+        <v>63</v>
+      </c>
+      <c r="D132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>103</v>
+      </c>
+      <c r="B133" t="s">
+        <v>47</v>
+      </c>
+      <c r="C133" t="s">
+        <v>48</v>
+      </c>
+      <c r="D133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>103</v>
+      </c>
+      <c r="B134" t="s">
+        <v>40</v>
+      </c>
+      <c r="C134" t="s">
+        <v>41</v>
+      </c>
+      <c r="D134" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>103</v>
+      </c>
+      <c r="B135" t="s">
+        <v>56</v>
+      </c>
+      <c r="C135" t="s">
+        <v>57</v>
+      </c>
+      <c r="D135" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>103</v>
+      </c>
+      <c r="B136" t="s">
+        <v>69</v>
+      </c>
+      <c r="C136" t="s">
+        <v>70</v>
+      </c>
+      <c r="D136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>103</v>
+      </c>
+      <c r="B137" t="s">
+        <v>33</v>
+      </c>
+      <c r="C137" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>103</v>
+      </c>
+      <c r="B138" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" t="s">
+        <v>16</v>
+      </c>
+      <c r="D138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>103</v>
+      </c>
+      <c r="B139" t="s">
+        <v>25</v>
+      </c>
+      <c r="C139" t="s">
+        <v>26</v>
+      </c>
+      <c r="D139" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>103</v>
+      </c>
+      <c r="B140" t="s">
+        <v>62</v>
+      </c>
+      <c r="C140" t="s">
+        <v>63</v>
+      </c>
+      <c r="D140" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
